--- a/Practicas Preprofesionales/horario_practicas.xlsx
+++ b/Practicas Preprofesionales/horario_practicas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ednan\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Josue\GitHub Personal\software-engineering\Practicas Preprofesionales\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="14">
   <si>
     <t>Lunes</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>08:00 - 18:00</t>
+  </si>
+  <si>
+    <t>Sandino</t>
   </si>
 </sst>
 </file>
@@ -387,6 +390,36 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -394,36 +427,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -706,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:Q46"/>
+  <dimension ref="C1:Q47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -718,20 +721,20 @@
   <sheetData>
     <row r="1" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="3:17" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="17"/>
-      <c r="K2" s="15" t="s">
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="27"/>
+      <c r="K2" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="17"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="27"/>
     </row>
     <row r="3" spans="3:17" s="8" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C3" s="7" t="s">
@@ -749,19 +752,19 @@
       <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L3" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="M3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="N3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="27" t="s">
+      <c r="O3" s="24" t="s">
         <v>4</v>
       </c>
     </row>
@@ -781,19 +784,19 @@
       <c r="G4" s="3">
         <v>29</v>
       </c>
-      <c r="K4" s="22">
+      <c r="K4" s="19">
         <v>1</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L4" s="20">
         <v>2</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="20">
         <v>3</v>
       </c>
-      <c r="N4" s="23">
+      <c r="N4" s="20">
         <v>4</v>
       </c>
-      <c r="O4" s="24">
+      <c r="O4" s="21">
         <v>5</v>
       </c>
     </row>
@@ -1320,16 +1323,16 @@
         <f>2*5</f>
         <v>10</v>
       </c>
-      <c r="K19" s="18" t="s">
+      <c r="K19" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="L19" s="19" t="s">
+      <c r="L19" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="M19" s="19" t="s">
+      <c r="M19" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="N19" s="19" t="s">
+      <c r="N19" s="16" t="s">
         <v>7</v>
       </c>
       <c r="O19" s="10" t="s">
@@ -1356,11 +1359,11 @@
       <c r="G20" s="6">
         <v>24</v>
       </c>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
     </row>
     <row r="21" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C21" s="4" t="s">
@@ -1382,11 +1385,11 @@
         <f>2*5</f>
         <v>10</v>
       </c>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1418,13 +1421,13 @@
     </row>
     <row r="25" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="3:17" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C26" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="17"/>
+      <c r="C26" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="27"/>
     </row>
     <row r="27" spans="3:17" ht="21" x14ac:dyDescent="0.4">
       <c r="C27" s="7" t="s">
@@ -1477,8 +1480,8 @@
         <v>5</v>
       </c>
       <c r="I29">
-        <f>8*5</f>
-        <v>40</v>
+        <f>6*5</f>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="3:17" x14ac:dyDescent="0.3">
@@ -1515,8 +1518,8 @@
         <v>5</v>
       </c>
       <c r="I31">
-        <f>8*5</f>
-        <v>40</v>
+        <f>6*5</f>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="3:17" x14ac:dyDescent="0.3">
@@ -1553,8 +1556,8 @@
         <v>5</v>
       </c>
       <c r="I33">
-        <f>8*5</f>
-        <v>40</v>
+        <f>6*5</f>
+        <v>30</v>
       </c>
       <c r="K33" t="s">
         <v>11</v>
@@ -1594,8 +1597,8 @@
         <v>5</v>
       </c>
       <c r="I35">
-        <f>8*5</f>
-        <v>40</v>
+        <f>6*5</f>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
@@ -1632,8 +1635,8 @@
         <v>5</v>
       </c>
       <c r="I37">
-        <f>8*5</f>
-        <v>40</v>
+        <f>6*5</f>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="3:11" x14ac:dyDescent="0.3">
@@ -1669,6 +1672,10 @@
       <c r="G39" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="I39">
+        <f>6*5</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="40" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C40" s="6">
@@ -1702,6 +1709,10 @@
       </c>
       <c r="G41" s="4" t="s">
         <v>6</v>
+      </c>
+      <c r="I41">
+        <f>6*4</f>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="3:11" x14ac:dyDescent="0.3">
@@ -1737,6 +1748,10 @@
       <c r="G43" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="I43">
+        <f>6*5</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="44" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C44" s="6">
@@ -1771,6 +1786,10 @@
       <c r="G45" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="I45">
+        <f>6*5</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="46" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C46" s="6">
@@ -1787,6 +1806,12 @@
       </c>
       <c r="G46" s="6">
         <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="I47">
+        <f>SUM(I29:I45)</f>
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/Practicas Preprofesionales/horario_practicas.xlsx
+++ b/Practicas Preprofesionales/horario_practicas.xlsx
@@ -112,7 +112,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -137,6 +137,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="15">
     <border>
@@ -346,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -427,6 +433,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -709,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:Q47"/>
+  <dimension ref="C1:Q46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -1690,7 +1702,7 @@
       <c r="F40" s="6">
         <v>9</v>
       </c>
-      <c r="G40" s="6">
+      <c r="G40" s="28">
         <v>10</v>
       </c>
     </row>
@@ -1707,7 +1719,7 @@
       <c r="F41" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="29" t="s">
         <v>6</v>
       </c>
       <c r="I41">
@@ -1792,24 +1804,7 @@
       </c>
     </row>
     <row r="46" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C46" s="6">
-        <v>27</v>
-      </c>
-      <c r="D46" s="6">
-        <v>28</v>
-      </c>
-      <c r="E46" s="6">
-        <v>29</v>
-      </c>
-      <c r="F46" s="6">
-        <v>30</v>
-      </c>
-      <c r="G46" s="6">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="I47">
+      <c r="I46">
         <f>SUM(I29:I45)</f>
         <v>264</v>
       </c>

--- a/Practicas Preprofesionales/horario_practicas.xlsx
+++ b/Practicas Preprofesionales/horario_practicas.xlsx
@@ -56,9 +56,6 @@
     <t>Hospital Militar</t>
   </si>
   <si>
-    <t>07:00 - 16:00</t>
-  </si>
-  <si>
     <t>.</t>
   </si>
   <si>
@@ -67,12 +64,15 @@
   <si>
     <t>Sandino</t>
   </si>
+  <si>
+    <t>14:00 - 20:00</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,6 +107,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -352,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -426,6 +433,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -435,10 +448,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -733,20 +743,20 @@
   <sheetData>
     <row r="1" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="3:17" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="27"/>
-      <c r="K2" s="25" t="s">
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29"/>
+      <c r="K2" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="27"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="29"/>
     </row>
     <row r="3" spans="3:17" s="8" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C3" s="7" t="s">
@@ -1204,7 +1214,7 @@
         <v>7</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q15" s="1">
         <f>6*5</f>
@@ -1276,7 +1286,7 @@
         <v>7</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q17" s="1">
         <f>6*5</f>
@@ -1348,7 +1358,7 @@
         <v>7</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q19" s="1">
         <f>6*5</f>
@@ -1433,13 +1443,13 @@
     </row>
     <row r="25" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="3:17" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C26" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="27"/>
+      <c r="C26" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="29"/>
     </row>
     <row r="27" spans="3:17" ht="21" x14ac:dyDescent="0.4">
       <c r="C27" s="7" t="s">
@@ -1477,19 +1487,19 @@
     </row>
     <row r="29" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C29" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I29">
         <f>6*5</f>
@@ -1515,19 +1525,19 @@
     </row>
     <row r="31" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C31" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I31">
         <f>6*5</f>
@@ -1553,26 +1563,26 @@
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C33" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I33">
         <f>6*5</f>
         <v>30</v>
       </c>
       <c r="K33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="3:11" x14ac:dyDescent="0.3">
@@ -1594,19 +1604,19 @@
     </row>
     <row r="35" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C35" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I35">
         <f>6*5</f>
@@ -1631,20 +1641,20 @@
       </c>
     </row>
     <row r="37" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C37" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>5</v>
+      <c r="C37" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="30" t="s">
+        <v>13</v>
       </c>
       <c r="I37">
         <f>6*5</f>
@@ -1669,20 +1679,20 @@
       </c>
     </row>
     <row r="39" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>5</v>
+      <c r="C39" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="30" t="s">
+        <v>13</v>
       </c>
       <c r="I39">
         <f>6*5</f>
@@ -1702,24 +1712,24 @@
       <c r="F40" s="6">
         <v>9</v>
       </c>
-      <c r="G40" s="28">
+      <c r="G40" s="25">
         <v>10</v>
       </c>
     </row>
     <row r="41" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C41" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G41" s="29" t="s">
+      <c r="C41" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="26" t="s">
         <v>6</v>
       </c>
       <c r="I41">
@@ -1745,20 +1755,20 @@
       </c>
     </row>
     <row r="43" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C43" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>6</v>
+      <c r="C43" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="30" t="s">
+        <v>13</v>
       </c>
       <c r="I43">
         <f>6*5</f>
@@ -1783,20 +1793,20 @@
       </c>
     </row>
     <row r="45" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C45" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>6</v>
+      <c r="C45" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="30" t="s">
+        <v>13</v>
       </c>
       <c r="I45">
         <f>6*5</f>
